--- a/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_pair_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_pair_profile_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,55 +451,65 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_D6</t>
+          <t>mean_D6_raw</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>median_D6</t>
+          <t>median_D6_raw</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>p05_D6</t>
+          <t>p05_D6_raw</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>mean_D6_provisional</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>evaluable_rate</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>deadband_rate</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>fuse_active_rate</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mean_Q_dist</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mean_Q_trend</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_Q_var</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_Q_cp</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>low_score_rate</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>evaluable_rate</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>deadband_rate</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>mean_Q_dist</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mean_Q_trend</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>mean_Q_var</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_Q_cp</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>n_events</t>
         </is>
@@ -527,16 +537,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.980884822028206</v>
+        <v>3.327004281396911</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1375</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>2.384375</v>
+        <v>1.6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1202417905570985</v>
+        <v>3.329984044339939</v>
       </c>
       <c r="I2" t="n">
         <v>0.9730436203234766</v>
@@ -545,19 +555,25 @@
         <v>0.2465283450416599</v>
       </c>
       <c r="K2" t="n">
-        <v>4.280836464629963</v>
+        <v>0.002940695964711648</v>
       </c>
       <c r="L2" t="n">
-        <v>4.130697598431629</v>
+        <v>3.644012416271851</v>
       </c>
       <c r="M2" t="n">
-        <v>4.187714425747427</v>
+        <v>4.035941839568698</v>
       </c>
       <c r="N2" t="n">
-        <v>4.052115667374612</v>
+        <v>4.02466917170397</v>
       </c>
       <c r="O2" t="n">
-        <v>76</v>
+        <v>2.771932690736808</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3326057756883815</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="3">
@@ -582,16 +598,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.988911623677249</v>
+        <v>3.33974041005291</v>
       </c>
       <c r="F3" t="n">
-        <v>4.125</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>1.9375</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1182813265806241</v>
+        <v>3.340497849818062</v>
       </c>
       <c r="I3" t="n">
         <v>0.9880738441431138</v>
@@ -600,19 +616,25 @@
         <v>0.006534879921581441</v>
       </c>
       <c r="K3" t="n">
-        <v>4.275445188694658</v>
+        <v>0.003104067962751185</v>
       </c>
       <c r="L3" t="n">
-        <v>4.184773729782715</v>
+        <v>4.078255187060938</v>
       </c>
       <c r="M3" t="n">
-        <v>4.178728965855252</v>
+        <v>4.025486031694167</v>
       </c>
       <c r="N3" t="n">
-        <v>4.139519686325764</v>
+        <v>3.770298970756413</v>
       </c>
       <c r="O3" t="n">
-        <v>89</v>
+        <v>2.623917660512988</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.289186507936508</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="4">
@@ -637,16 +659,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.787562003968254</v>
+        <v>3.139785879629629</v>
       </c>
       <c r="F4" t="n">
-        <v>3.825</v>
+        <v>3.1375</v>
       </c>
       <c r="G4" t="n">
-        <v>2.35</v>
+        <v>1.825</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1707237379513152</v>
+        <v>3.14209394641085</v>
       </c>
       <c r="I4" t="n">
         <v>0.9880738441431138</v>
@@ -655,19 +677,25 @@
         <v>0.000326743996079072</v>
       </c>
       <c r="K4" t="n">
-        <v>4.025322659696128</v>
+        <v>0.003594183956869793</v>
       </c>
       <c r="L4" t="n">
-        <v>4.046397647443229</v>
+        <v>3.811632086260415</v>
       </c>
       <c r="M4" t="n">
-        <v>3.947394216631269</v>
+        <v>3.822578010129064</v>
       </c>
       <c r="N4" t="n">
-        <v>4.075314491096226</v>
+        <v>3.360071883679137</v>
       </c>
       <c r="O4" t="n">
-        <v>135</v>
+        <v>2.76409083483091</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4345238095238095</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="5">
@@ -692,16 +720,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.033933591004919</v>
+        <v>3.13829936753338</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3375</v>
+        <v>3.1625</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4125</v>
+        <v>1.75</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03332788760006535</v>
+        <v>3.138571679550246</v>
       </c>
       <c r="I5" t="n">
         <v>0.2324783532102598</v>
@@ -710,19 +738,25 @@
         <v>0.657408920111093</v>
       </c>
       <c r="K5" t="n">
-        <v>3.847573925829113</v>
+        <v>0.007024995915700049</v>
       </c>
       <c r="L5" t="n">
-        <v>4.236235909165169</v>
+        <v>2.806077438327071</v>
       </c>
       <c r="M5" t="n">
-        <v>4.015030223819637</v>
+        <v>4.195392909655285</v>
       </c>
       <c r="N5" t="n">
-        <v>4.116810978598268</v>
+        <v>3.929259924848881</v>
       </c>
       <c r="O5" t="n">
-        <v>36</v>
+        <v>2.42607417088711</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4300773014757555</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -747,16 +781,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.78417149376865</v>
+        <v>3.487706248902932</v>
       </c>
       <c r="F6" t="n">
-        <v>3.825</v>
+        <v>3.4875</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3125</v>
+        <v>2.1625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1757882698905407</v>
+        <v>3.487449517120281</v>
       </c>
       <c r="I6" t="n">
         <v>0.9307302728312368</v>
@@ -765,19 +799,25 @@
         <v>0.2238196373141643</v>
       </c>
       <c r="K6" t="n">
-        <v>3.960463976474432</v>
+        <v>0.001143603986276752</v>
       </c>
       <c r="L6" t="n">
-        <v>4.049501715405979</v>
+        <v>3.912595981048848</v>
       </c>
       <c r="M6" t="n">
-        <v>4.002613951968633</v>
+        <v>4.283613788596634</v>
       </c>
       <c r="N6" t="n">
-        <v>4.097042966835485</v>
+        <v>3.847900669825192</v>
       </c>
       <c r="O6" t="n">
-        <v>169</v>
+        <v>3.139356314327724</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.257152887484641</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="7">
@@ -802,16 +842,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.771660846791794</v>
+        <v>3.150308271497163</v>
       </c>
       <c r="F7" t="n">
-        <v>3.825</v>
+        <v>3.125</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1625</v>
+        <v>1.825</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1488318902140173</v>
+        <v>3.15056470973374</v>
       </c>
       <c r="I7" t="n">
         <v>0.7485704950171541</v>
@@ -820,19 +860,25 @@
         <v>0.02728312367260251</v>
       </c>
       <c r="K7" t="n">
-        <v>3.572618853128574</v>
+        <v>0.0163371998039536</v>
       </c>
       <c r="L7" t="n">
-        <v>4.022055219735337</v>
+        <v>3.074497631106028</v>
       </c>
       <c r="M7" t="n">
-        <v>3.608233948701193</v>
+        <v>4.064531939225617</v>
       </c>
       <c r="N7" t="n">
-        <v>4.090181342917824</v>
+        <v>2.568371181179546</v>
       </c>
       <c r="O7" t="n">
-        <v>121</v>
+        <v>3.529488645646136</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4646442601484068</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>142</v>
       </c>
     </row>
     <row r="8">
@@ -857,16 +903,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.873839738941261</v>
+        <v>2.759001087744742</v>
       </c>
       <c r="F8" t="n">
-        <v>3.9375</v>
+        <v>2.675</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6125</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09459238686489135</v>
+        <v>2.758808948004837</v>
       </c>
       <c r="I8" t="n">
         <v>0.6758699558895606</v>
@@ -875,19 +921,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.009148831890214</v>
+        <v>0.000980231988237216</v>
       </c>
       <c r="L8" t="n">
-        <v>4.154386538147362</v>
+        <v>2.949681424603823</v>
       </c>
       <c r="M8" t="n">
-        <v>3.892827969286064</v>
+        <v>3.520829929750041</v>
       </c>
       <c r="N8" t="n">
-        <v>4.170723737951315</v>
+        <v>2.439634046724391</v>
       </c>
       <c r="O8" t="n">
-        <v>79</v>
+        <v>2.840222185917334</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.6325839980662316</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_pair_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_pair_profile_summary.xlsx
@@ -537,16 +537,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.327004281396911</v>
+        <v>3.310613247145735</v>
       </c>
       <c r="F2" t="n">
         <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6</v>
+        <v>1.6375</v>
       </c>
       <c r="H2" t="n">
-        <v>3.329984044339939</v>
+        <v>3.313430047027208</v>
       </c>
       <c r="I2" t="n">
         <v>0.9730436203234766</v>
@@ -558,19 +558,19 @@
         <v>0.002940695964711648</v>
       </c>
       <c r="L2" t="n">
-        <v>3.644012416271851</v>
+        <v>3.582094429014867</v>
       </c>
       <c r="M2" t="n">
-        <v>4.035941839568698</v>
+        <v>4.018297663780428</v>
       </c>
       <c r="N2" t="n">
-        <v>4.02466917170397</v>
+        <v>4.054566247345205</v>
       </c>
       <c r="O2" t="n">
         <v>2.771932690736808</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3326057756883815</v>
+        <v>0.3446944257891202</v>
       </c>
       <c r="Q2" t="n">
         <v>126</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.33974041005291</v>
+        <v>3.357345403439153</v>
       </c>
       <c r="F3" t="n">
         <v>3.4</v>
@@ -607,7 +607,7 @@
         <v>1.9375</v>
       </c>
       <c r="H3" t="n">
-        <v>3.340497849818062</v>
+        <v>3.357974280516044</v>
       </c>
       <c r="I3" t="n">
         <v>0.9880738441431138</v>
@@ -616,25 +616,25 @@
         <v>0.006534879921581441</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003104067962751185</v>
+        <v>0.00326743996079072</v>
       </c>
       <c r="L3" t="n">
-        <v>4.078255187060938</v>
+        <v>4.039209279529489</v>
       </c>
       <c r="M3" t="n">
-        <v>4.025486031694167</v>
+        <v>4.004737787943147</v>
       </c>
       <c r="N3" t="n">
-        <v>3.770298970756413</v>
+        <v>3.915700049011599</v>
       </c>
       <c r="O3" t="n">
         <v>2.623917660512988</v>
       </c>
       <c r="P3" t="n">
-        <v>0.289186507936508</v>
+        <v>0.2800925925925926</v>
       </c>
       <c r="Q3" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.139785879629629</v>
+        <v>3.159441137566137</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1375</v>
+        <v>3.1625</v>
       </c>
       <c r="G4" t="n">
-        <v>1.825</v>
+        <v>1.8625</v>
       </c>
       <c r="H4" t="n">
-        <v>3.14209394641085</v>
+        <v>3.161904565001654</v>
       </c>
       <c r="I4" t="n">
         <v>0.9880738441431138</v>
@@ -677,25 +677,25 @@
         <v>0.000326743996079072</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003594183956869793</v>
+        <v>0.00326743996079072</v>
       </c>
       <c r="L4" t="n">
-        <v>3.811632086260415</v>
+        <v>3.790883842509394</v>
       </c>
       <c r="M4" t="n">
-        <v>3.822578010129064</v>
+        <v>3.796601862440778</v>
       </c>
       <c r="N4" t="n">
-        <v>3.360071883679137</v>
+        <v>3.498774710014704</v>
       </c>
       <c r="O4" t="n">
         <v>2.76409083483091</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4345238095238095</v>
+        <v>0.4246031746031746</v>
       </c>
       <c r="Q4" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.13829936753338</v>
+        <v>3.139959592410401</v>
       </c>
       <c r="F5" t="n">
         <v>3.1625</v>
@@ -729,7 +729,7 @@
         <v>1.75</v>
       </c>
       <c r="H5" t="n">
-        <v>3.138571679550246</v>
+        <v>3.139959592410401</v>
       </c>
       <c r="I5" t="n">
         <v>0.2324783532102598</v>
@@ -738,22 +738,22 @@
         <v>0.657408920111093</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007024995915700049</v>
+        <v>0.004247671949027937</v>
       </c>
       <c r="L5" t="n">
-        <v>2.806077438327071</v>
+        <v>2.729455971246528</v>
       </c>
       <c r="M5" t="n">
-        <v>4.195392909655285</v>
+        <v>4.188204541741546</v>
       </c>
       <c r="N5" t="n">
-        <v>3.929259924848881</v>
+        <v>3.946413984643032</v>
       </c>
       <c r="O5" t="n">
         <v>2.42607417088711</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4300773014757555</v>
+        <v>0.4237526352775826</v>
       </c>
       <c r="Q5" t="n">
         <v>40</v>
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.487706248902932</v>
+        <v>3.528629103036686</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4875</v>
+        <v>3.5375</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1625</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.487449517120281</v>
+        <v>3.528292361720808</v>
       </c>
       <c r="I6" t="n">
         <v>0.9307302728312368</v>
@@ -799,25 +799,25 @@
         <v>0.2238196373141643</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001143603986276752</v>
+        <v>0.000980231988237216</v>
       </c>
       <c r="L6" t="n">
-        <v>3.912595981048848</v>
+        <v>3.959647116484235</v>
       </c>
       <c r="M6" t="n">
-        <v>4.283613788596634</v>
+        <v>4.203234765561183</v>
       </c>
       <c r="N6" t="n">
-        <v>3.847900669825192</v>
+        <v>4.030550563633393</v>
       </c>
       <c r="O6" t="n">
         <v>3.139356314327724</v>
       </c>
       <c r="P6" t="n">
-        <v>0.257152887484641</v>
+        <v>0.2352115148323679</v>
       </c>
       <c r="Q6" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
@@ -842,16 +842,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.150308271497163</v>
+        <v>3.205698930597992</v>
       </c>
       <c r="F7" t="n">
-        <v>3.125</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.825</v>
+        <v>1.8625</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15056470973374</v>
+        <v>3.205857158446093</v>
       </c>
       <c r="I7" t="n">
         <v>0.7485704950171541</v>
@@ -860,25 +860,25 @@
         <v>0.02728312367260251</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0163371998039536</v>
+        <v>0.006044763927462833</v>
       </c>
       <c r="L7" t="n">
-        <v>3.074497631106028</v>
+        <v>3.084136578990361</v>
       </c>
       <c r="M7" t="n">
-        <v>4.064531939225617</v>
+        <v>3.984316288188205</v>
       </c>
       <c r="N7" t="n">
-        <v>2.568371181179546</v>
+        <v>2.787453030550564</v>
       </c>
       <c r="O7" t="n">
         <v>3.529488645646136</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4646442601484068</v>
+        <v>0.424923614142296</v>
       </c>
       <c r="Q7" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.759001087744742</v>
+        <v>2.774332245588591</v>
       </c>
       <c r="F8" t="n">
-        <v>2.675</v>
+        <v>2.7125</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.525</v>
       </c>
       <c r="H8" t="n">
-        <v>2.758808948004837</v>
+        <v>2.774156590084643</v>
       </c>
       <c r="I8" t="n">
         <v>0.6758699558895606</v>
@@ -921,25 +921,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000980231988237216</v>
+        <v>0.00163371998039536</v>
       </c>
       <c r="L8" t="n">
-        <v>2.949681424603823</v>
+        <v>2.913902957033164</v>
       </c>
       <c r="M8" t="n">
-        <v>3.520829929750041</v>
+        <v>3.415781735010619</v>
       </c>
       <c r="N8" t="n">
-        <v>2.439634046724391</v>
+        <v>2.621630452540435</v>
       </c>
       <c r="O8" t="n">
         <v>2.840222185917334</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6325839980662316</v>
+        <v>0.6154218032390621</v>
       </c>
       <c r="Q8" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_pair_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_pair_profile_summary.xlsx
@@ -537,19 +537,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.310613247145735</v>
+        <v>3.367710252973697</v>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6375</v>
+        <v>1.75</v>
       </c>
       <c r="H2" t="n">
-        <v>3.313430047027208</v>
+        <v>3.367741327300151</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9730436203234766</v>
+        <v>0.9751674562979905</v>
       </c>
       <c r="J2" t="n">
         <v>0.2465283450416599</v>
@@ -558,22 +558,22 @@
         <v>0.002940695964711648</v>
       </c>
       <c r="L2" t="n">
-        <v>3.582094429014867</v>
+        <v>3.699885639601372</v>
       </c>
       <c r="M2" t="n">
-        <v>4.018297663780428</v>
+        <v>4.034308119588302</v>
       </c>
       <c r="N2" t="n">
-        <v>4.054566247345205</v>
+        <v>4.136415618363013</v>
       </c>
       <c r="O2" t="n">
         <v>2.771932690736808</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3446944257891202</v>
+        <v>0.3141229686714693</v>
       </c>
       <c r="Q2" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.357345403439153</v>
+        <v>3.391024156187955</v>
       </c>
       <c r="F3" t="n">
         <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9375</v>
+        <v>2.0125</v>
       </c>
       <c r="H3" t="n">
-        <v>3.357974280516044</v>
+        <v>3.39073361469712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9880738441431138</v>
+        <v>0.9874203561509557</v>
       </c>
       <c r="J3" t="n">
         <v>0.006534879921581441</v>
@@ -619,22 +619,22 @@
         <v>0.00326743996079072</v>
       </c>
       <c r="L3" t="n">
-        <v>4.039209279529489</v>
+        <v>4.109785982682568</v>
       </c>
       <c r="M3" t="n">
-        <v>4.004737787943147</v>
+        <v>4.019768011762784</v>
       </c>
       <c r="N3" t="n">
-        <v>3.915700049011599</v>
+        <v>3.958176768501879</v>
       </c>
       <c r="O3" t="n">
         <v>2.623917660512988</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2800925925925926</v>
+        <v>0.264559894109861</v>
       </c>
       <c r="Q3" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.159441137566137</v>
+        <v>3.19844499586435</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1625</v>
+        <v>3.2125</v>
       </c>
       <c r="G4" t="n">
         <v>1.8625</v>
       </c>
       <c r="H4" t="n">
-        <v>3.161904565001654</v>
+        <v>3.199261542280325</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9880738441431138</v>
+        <v>0.9875837281489953</v>
       </c>
       <c r="J4" t="n">
         <v>0.000326743996079072</v>
@@ -680,22 +680,22 @@
         <v>0.00326743996079072</v>
       </c>
       <c r="L4" t="n">
-        <v>3.790883842509394</v>
+        <v>3.857702989707564</v>
       </c>
       <c r="M4" t="n">
-        <v>3.796601862440778</v>
+        <v>3.817186734193759</v>
       </c>
       <c r="N4" t="n">
-        <v>3.498774710014704</v>
+        <v>3.559385721287371</v>
       </c>
       <c r="O4" t="n">
         <v>2.76409083483091</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4246031746031746</v>
+        <v>0.4059553349875931</v>
       </c>
       <c r="Q4" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5">
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.139959592410401</v>
+        <v>2.977698511166253</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1625</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.75</v>
+        <v>1.5325</v>
       </c>
       <c r="H5" t="n">
-        <v>3.139959592410401</v>
+        <v>2.979575541949363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2324783532102598</v>
+        <v>0.9875837281489953</v>
       </c>
       <c r="J5" t="n">
         <v>0.657408920111093</v>
@@ -741,22 +741,22 @@
         <v>0.004247671949027937</v>
       </c>
       <c r="L5" t="n">
-        <v>2.729455971246528</v>
+        <v>2.899852965201764</v>
       </c>
       <c r="M5" t="n">
-        <v>4.188204541741546</v>
+        <v>4.202908021565103</v>
       </c>
       <c r="N5" t="n">
-        <v>3.946413984643032</v>
+        <v>4.013396503839242</v>
       </c>
       <c r="O5" t="n">
         <v>2.42607417088711</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4237526352775826</v>
+        <v>0.4775847808105873</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.528629103036686</v>
+        <v>3.425426991150442</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5375</v>
+        <v>3.425</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.528292361720808</v>
+        <v>3.425050902974504</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9307302728312368</v>
+        <v>0.9230517889233786</v>
       </c>
       <c r="J6" t="n">
         <v>0.2238196373141643</v>
@@ -802,22 +802,22 @@
         <v>0.000980231988237216</v>
       </c>
       <c r="L6" t="n">
-        <v>3.959647116484235</v>
+        <v>3.847247181833034</v>
       </c>
       <c r="M6" t="n">
-        <v>4.203234765561183</v>
+        <v>4.062408103251102</v>
       </c>
       <c r="N6" t="n">
-        <v>4.030550563633393</v>
+        <v>3.949191308609704</v>
       </c>
       <c r="O6" t="n">
         <v>3.139356314327724</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2352115148323679</v>
+        <v>0.2766371681415929</v>
       </c>
       <c r="Q6" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.205698930597992</v>
+        <v>3.04028584708343</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3.0125</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8625</v>
+        <v>1.675</v>
       </c>
       <c r="H7" t="n">
-        <v>3.205857158446093</v>
+        <v>3.04028584708343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7485704950171541</v>
+        <v>0.7029897075641235</v>
       </c>
       <c r="J7" t="n">
         <v>0.02728312367260251</v>
@@ -863,22 +863,22 @@
         <v>0.006044763927462833</v>
       </c>
       <c r="L7" t="n">
-        <v>3.084136578990361</v>
+        <v>2.901159941186081</v>
       </c>
       <c r="M7" t="n">
-        <v>3.984316288188205</v>
+        <v>3.822251266132985</v>
       </c>
       <c r="N7" t="n">
-        <v>2.787453030550564</v>
+        <v>2.713608887436693</v>
       </c>
       <c r="O7" t="n">
         <v>3.529488645646136</v>
       </c>
       <c r="P7" t="n">
-        <v>0.424923614142296</v>
+        <v>0.4924471299093656</v>
       </c>
       <c r="Q7" t="n">
-        <v>135</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.774332245588591</v>
+        <v>2.649996820147545</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7125</v>
+        <v>2.5625</v>
       </c>
       <c r="G8" t="n">
-        <v>1.525</v>
+        <v>1.45</v>
       </c>
       <c r="H8" t="n">
-        <v>2.774156590084643</v>
+        <v>2.64978684143548</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6758699558895606</v>
+        <v>0.6422153242934161</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -924,22 +924,22 @@
         <v>0.00163371998039536</v>
       </c>
       <c r="L8" t="n">
-        <v>2.913902957033164</v>
+        <v>2.73256003920928</v>
       </c>
       <c r="M8" t="n">
-        <v>3.415781735010619</v>
+        <v>3.207155693514132</v>
       </c>
       <c r="N8" t="n">
-        <v>2.621630452540435</v>
+        <v>2.557915373305016</v>
       </c>
       <c r="O8" t="n">
         <v>2.840222185917334</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6154218032390621</v>
+        <v>0.6761638259984737</v>
       </c>
       <c r="Q8" t="n">
-        <v>131</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
